--- a/translators/xlsx/tests/sample_fontstyle.xlsx
+++ b/translators/xlsx/tests/sample_fontstyle.xlsx
@@ -11,7 +11,6 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="5">
     <font>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -21,7 +20,6 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -32,7 +30,6 @@
     </font>
     <font>
       <b val="0"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
